--- a/output/Supplier Configuration.xlsx
+++ b/output/Supplier Configuration.xlsx
@@ -56787,124 +56787,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK8"/>
+  <dimension ref="A1:DN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26.4" customWidth="1" min="1" max="1"/>
-    <col width="8.4" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="33.6" customWidth="1" min="5" max="5"/>
-    <col width="31.2" customWidth="1" min="6" max="6"/>
-    <col width="21.6" customWidth="1" min="7" max="7"/>
-    <col width="10.8" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="19.2" customWidth="1" min="10" max="10"/>
-    <col width="14.4" customWidth="1" min="11" max="11"/>
-    <col width="10.8" customWidth="1" min="12" max="12"/>
-    <col width="21.6" customWidth="1" min="13" max="13"/>
-    <col width="16.8" customWidth="1" min="14" max="14"/>
-    <col width="33.6" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26.4" customWidth="1" min="2" max="2"/>
+    <col width="8.4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="33.6" customWidth="1" min="6" max="6"/>
+    <col width="31.2" customWidth="1" min="7" max="7"/>
+    <col width="21.6" customWidth="1" min="8" max="8"/>
+    <col width="10.8" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="19.2" customWidth="1" min="11" max="11"/>
+    <col width="14.4" customWidth="1" min="12" max="12"/>
+    <col width="10.8" customWidth="1" min="13" max="13"/>
+    <col width="21.6" customWidth="1" min="14" max="14"/>
+    <col width="16.8" customWidth="1" min="15" max="15"/>
+    <col width="33.6" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="34.8" customWidth="1" min="18" max="18"/>
-    <col width="16.8" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="7.199999999999999" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="34.8" customWidth="1" min="19" max="19"/>
+    <col width="16.8" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="7.199999999999999" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="13.2" customWidth="1" min="29" max="29"/>
-    <col width="19.2" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="26.4" customWidth="1" min="32" max="32"/>
-    <col width="31.2" customWidth="1" min="33" max="33"/>
-    <col width="28.8" customWidth="1" min="34" max="34"/>
-    <col width="26.4" customWidth="1" min="35" max="35"/>
-    <col width="31.2" customWidth="1" min="36" max="36"/>
-    <col width="28.8" customWidth="1" min="37" max="37"/>
-    <col width="26.4" customWidth="1" min="38" max="38"/>
-    <col width="31.2" customWidth="1" min="39" max="39"/>
-    <col width="28.8" customWidth="1" min="40" max="40"/>
-    <col width="42" customWidth="1" min="41" max="41"/>
-    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="26.4" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="13.2" customWidth="1" min="30" max="30"/>
+    <col width="19.2" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="26.4" customWidth="1" min="33" max="33"/>
+    <col width="31.2" customWidth="1" min="34" max="34"/>
+    <col width="28.8" customWidth="1" min="35" max="35"/>
+    <col width="26.4" customWidth="1" min="36" max="36"/>
+    <col width="31.2" customWidth="1" min="37" max="37"/>
+    <col width="28.8" customWidth="1" min="38" max="38"/>
+    <col width="26.4" customWidth="1" min="39" max="39"/>
+    <col width="31.2" customWidth="1" min="40" max="40"/>
+    <col width="28.8" customWidth="1" min="41" max="41"/>
+    <col width="42" customWidth="1" min="42" max="42"/>
     <col width="18" customWidth="1" min="43" max="43"/>
-    <col width="24" customWidth="1" min="44" max="44"/>
-    <col width="14.4" customWidth="1" min="45" max="45"/>
-    <col width="18" customWidth="1" min="46" max="46"/>
-    <col width="36" customWidth="1" min="47" max="47"/>
-    <col width="16.8" customWidth="1" min="48" max="48"/>
-    <col width="27.6" customWidth="1" min="49" max="49"/>
-    <col width="19.2" customWidth="1" min="50" max="50"/>
-    <col width="20.4" customWidth="1" min="51" max="51"/>
-    <col width="36" customWidth="1" min="52" max="52"/>
-    <col width="25.2" customWidth="1" min="53" max="53"/>
-    <col width="34.8" customWidth="1" min="54" max="54"/>
-    <col width="27.6" customWidth="1" min="55" max="55"/>
-    <col width="20.4" customWidth="1" min="56" max="56"/>
-    <col width="26.4" customWidth="1" min="57" max="57"/>
-    <col width="22.8" customWidth="1" min="58" max="58"/>
-    <col width="15.6" customWidth="1" min="59" max="59"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="14.4" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="48" max="48"/>
+    <col width="16.8" customWidth="1" min="49" max="49"/>
+    <col width="27.6" customWidth="1" min="50" max="50"/>
+    <col width="19.2" customWidth="1" min="51" max="51"/>
+    <col width="20.4" customWidth="1" min="52" max="52"/>
+    <col width="36" customWidth="1" min="53" max="53"/>
+    <col width="25.2" customWidth="1" min="54" max="54"/>
+    <col width="34.8" customWidth="1" min="55" max="55"/>
+    <col width="27.6" customWidth="1" min="56" max="56"/>
+    <col width="20.4" customWidth="1" min="57" max="57"/>
+    <col width="26.4" customWidth="1" min="58" max="58"/>
+    <col width="22.8" customWidth="1" min="59" max="59"/>
     <col width="15.6" customWidth="1" min="60" max="60"/>
     <col width="15.6" customWidth="1" min="61" max="61"/>
-    <col width="16.8" customWidth="1" min="62" max="62"/>
-    <col width="20.4" customWidth="1" min="63" max="63"/>
-    <col width="8.4" customWidth="1" min="64" max="64"/>
-    <col width="14.4" customWidth="1" min="65" max="65"/>
-    <col width="19.2" customWidth="1" min="66" max="66"/>
-    <col width="27.6" customWidth="1" min="67" max="67"/>
-    <col width="15.6" customWidth="1" min="68" max="68"/>
-    <col width="14.4" customWidth="1" min="69" max="69"/>
-    <col width="12" customWidth="1" min="70" max="70"/>
-    <col width="21.6" customWidth="1" min="71" max="71"/>
-    <col width="19.2" customWidth="1" min="72" max="72"/>
-    <col width="31.2" customWidth="1" min="73" max="73"/>
-    <col width="18" customWidth="1" min="74" max="74"/>
-    <col width="20.4" customWidth="1" min="75" max="75"/>
-    <col width="18" customWidth="1" min="76" max="76"/>
-    <col width="19.2" customWidth="1" min="77" max="77"/>
-    <col width="18" customWidth="1" min="78" max="78"/>
-    <col width="30" customWidth="1" min="79" max="79"/>
-    <col width="18" customWidth="1" min="80" max="80"/>
-    <col width="21.6" customWidth="1" min="81" max="81"/>
-    <col width="28.8" customWidth="1" min="82" max="82"/>
-    <col width="7.199999999999999" customWidth="1" min="83" max="83"/>
-    <col width="27.6" customWidth="1" min="84" max="84"/>
-    <col width="22.8" customWidth="1" min="85" max="85"/>
-    <col width="16.8" customWidth="1" min="86" max="86"/>
-    <col width="36" customWidth="1" min="87" max="87"/>
-    <col width="32.4" customWidth="1" min="88" max="88"/>
+    <col width="15.6" customWidth="1" min="62" max="62"/>
+    <col width="16.8" customWidth="1" min="63" max="63"/>
+    <col width="20.4" customWidth="1" min="64" max="64"/>
+    <col width="8.4" customWidth="1" min="65" max="65"/>
+    <col width="14.4" customWidth="1" min="66" max="66"/>
+    <col width="19.2" customWidth="1" min="67" max="67"/>
+    <col width="27.6" customWidth="1" min="68" max="68"/>
+    <col width="15.6" customWidth="1" min="69" max="69"/>
+    <col width="14.4" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="21.6" customWidth="1" min="72" max="72"/>
+    <col width="19.2" customWidth="1" min="73" max="73"/>
+    <col width="31.2" customWidth="1" min="74" max="74"/>
+    <col width="18" customWidth="1" min="75" max="75"/>
+    <col width="20.4" customWidth="1" min="76" max="76"/>
+    <col width="18" customWidth="1" min="77" max="77"/>
+    <col width="19.2" customWidth="1" min="78" max="78"/>
+    <col width="18" customWidth="1" min="79" max="79"/>
+    <col width="30" customWidth="1" min="80" max="80"/>
+    <col width="18" customWidth="1" min="81" max="81"/>
+    <col width="21.6" customWidth="1" min="82" max="82"/>
+    <col width="28.8" customWidth="1" min="83" max="83"/>
+    <col width="7.199999999999999" customWidth="1" min="84" max="84"/>
+    <col width="27.6" customWidth="1" min="85" max="85"/>
+    <col width="22.8" customWidth="1" min="86" max="86"/>
+    <col width="16.8" customWidth="1" min="87" max="87"/>
+    <col width="36" customWidth="1" min="88" max="88"/>
     <col width="32.4" customWidth="1" min="89" max="89"/>
     <col width="32.4" customWidth="1" min="90" max="90"/>
     <col width="32.4" customWidth="1" min="91" max="91"/>
     <col width="32.4" customWidth="1" min="92" max="92"/>
-    <col width="19.2" customWidth="1" min="93" max="93"/>
-    <col width="36" customWidth="1" min="94" max="94"/>
-    <col width="25.2" customWidth="1" min="95" max="95"/>
-    <col width="30" customWidth="1" min="96" max="96"/>
-    <col width="31.2" customWidth="1" min="97" max="97"/>
-    <col width="25.2" customWidth="1" min="98" max="98"/>
-    <col width="39.6" customWidth="1" min="99" max="99"/>
-    <col width="27.6" customWidth="1" min="100" max="100"/>
-    <col width="32.4" customWidth="1" min="101" max="101"/>
-    <col width="28.8" customWidth="1" min="102" max="102"/>
-    <col width="48" customWidth="1" min="103" max="103"/>
-    <col width="7.199999999999999" customWidth="1" min="104" max="104"/>
-    <col width="27.6" customWidth="1" min="105" max="105"/>
-    <col width="26.4" customWidth="1" min="106" max="106"/>
-    <col width="40.8" customWidth="1" min="107" max="107"/>
-    <col width="32.4" customWidth="1" min="108" max="108"/>
-    <col width="30" customWidth="1" min="109" max="109"/>
-    <col width="38.4" customWidth="1" min="110" max="110"/>
-    <col width="12" customWidth="1" min="111" max="111"/>
-    <col width="34.8" customWidth="1" min="112" max="112"/>
-    <col width="43.2" customWidth="1" min="113" max="113"/>
-    <col width="37.2" customWidth="1" min="114" max="114"/>
-    <col width="46.8" customWidth="1" min="115" max="115"/>
+    <col width="32.4" customWidth="1" min="93" max="93"/>
+    <col width="19.2" customWidth="1" min="94" max="94"/>
+    <col width="36" customWidth="1" min="95" max="95"/>
+    <col width="25.2" customWidth="1" min="96" max="96"/>
+    <col width="30" customWidth="1" min="97" max="97"/>
+    <col width="31.2" customWidth="1" min="98" max="98"/>
+    <col width="25.2" customWidth="1" min="99" max="99"/>
+    <col width="39.6" customWidth="1" min="100" max="100"/>
+    <col width="27.6" customWidth="1" min="101" max="101"/>
+    <col width="32.4" customWidth="1" min="102" max="102"/>
+    <col width="28.8" customWidth="1" min="103" max="103"/>
+    <col width="48" customWidth="1" min="104" max="104"/>
+    <col width="7.199999999999999" customWidth="1" min="105" max="105"/>
+    <col width="27.6" customWidth="1" min="106" max="106"/>
+    <col width="26.4" customWidth="1" min="107" max="107"/>
+    <col width="40.8" customWidth="1" min="108" max="108"/>
+    <col width="32.4" customWidth="1" min="109" max="109"/>
+    <col width="30" customWidth="1" min="110" max="110"/>
+    <col width="38.4" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="34.8" customWidth="1" min="113" max="113"/>
+    <col width="43.2" customWidth="1" min="114" max="114"/>
+    <col width="37.2" customWidth="1" min="115" max="115"/>
+    <col width="46.8" customWidth="1" min="116" max="116"/>
+    <col width="48" customWidth="1" min="117" max="117"/>
+    <col width="40.8" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -56931,2308 +56934,2368 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
           <t>Invoice batch number</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Payee</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Supplier invoice number</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Invoice batch header error</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Invoice batch line error</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Invoice progress</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Printed</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Invoice batch type</t>
         </is>
       </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Invoice status</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>Message ID</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="N5" s="27" t="inlineStr">
         <is>
           <t>Invoice matching</t>
         </is>
       </c>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t>Entry method</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="P5" s="27" t="inlineStr">
         <is>
           <t>EAN location code supplier</t>
         </is>
       </c>
-      <c r="P5" s="27" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t>VAT registration number</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="R5" s="27" t="inlineStr">
         <is>
           <t>EAN location code payee</t>
         </is>
       </c>
-      <c r="R5" s="27" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
         <is>
           <t>EAN location code consignee</t>
         </is>
       </c>
-      <c r="S5" s="27" t="inlineStr">
+      <c r="T5" s="27" t="inlineStr">
         <is>
           <t>Invoice date</t>
         </is>
       </c>
-      <c r="T5" s="27" t="inlineStr">
+      <c r="U5" s="27" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
-      <c r="U5" s="27" t="inlineStr">
+      <c r="V5" s="27" t="inlineStr">
         <is>
           <t>Document code</t>
         </is>
       </c>
-      <c r="V5" s="27" t="inlineStr">
+      <c r="W5" s="27" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="W5" s="27" t="inlineStr">
+      <c r="X5" s="27" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="X5" s="27" t="inlineStr">
+      <c r="Y5" s="27" t="inlineStr">
         <is>
           <t>Foreign currency amount</t>
         </is>
       </c>
-      <c r="Y5" s="27" t="inlineStr">
+      <c r="Z5" s="27" t="inlineStr">
         <is>
           <t>Total line amount - net</t>
         </is>
       </c>
-      <c r="Z5" s="27" t="inlineStr">
+      <c r="AA5" s="27" t="inlineStr">
         <is>
           <t>Cash discount base</t>
         </is>
       </c>
-      <c r="AA5" s="27" t="inlineStr">
+      <c r="AB5" s="27" t="inlineStr">
         <is>
           <t>Total taxable amount</t>
         </is>
       </c>
-      <c r="AB5" s="27" t="inlineStr">
+      <c r="AC5" s="27" t="inlineStr">
         <is>
           <t>Total charges</t>
         </is>
       </c>
-      <c r="AC5" s="27" t="inlineStr">
+      <c r="AD5" s="27" t="inlineStr">
         <is>
           <t>Total due</t>
         </is>
       </c>
-      <c r="AD5" s="27" t="inlineStr">
+      <c r="AE5" s="27" t="inlineStr">
         <is>
           <t>Prepaid amount</t>
         </is>
       </c>
-      <c r="AE5" s="27" t="inlineStr">
+      <c r="AF5" s="27" t="inlineStr">
         <is>
           <t>Cash discount term</t>
         </is>
       </c>
-      <c r="AF5" s="27" t="inlineStr">
+      <c r="AG5" s="27" t="inlineStr">
         <is>
           <t>Cash discount date 1</t>
         </is>
       </c>
-      <c r="AG5" s="27" t="inlineStr">
+      <c r="AH5" s="27" t="inlineStr">
         <is>
           <t>Cash discount percentage</t>
         </is>
       </c>
-      <c r="AH5" s="27" t="inlineStr">
+      <c r="AI5" s="27" t="inlineStr">
         <is>
           <t>Cash discount amount 1</t>
         </is>
       </c>
-      <c r="AI5" s="27" t="inlineStr">
+      <c r="AJ5" s="27" t="inlineStr">
         <is>
           <t>Cash discount date 2</t>
         </is>
       </c>
-      <c r="AJ5" s="27" t="inlineStr">
+      <c r="AK5" s="27" t="inlineStr">
         <is>
           <t>Cash discount percentage</t>
         </is>
       </c>
-      <c r="AK5" s="27" t="inlineStr">
+      <c r="AL5" s="27" t="inlineStr">
         <is>
           <t>Cash discount amount 2</t>
         </is>
       </c>
-      <c r="AL5" s="27" t="inlineStr">
+      <c r="AM5" s="27" t="inlineStr">
         <is>
           <t>Cash discount date 3</t>
         </is>
       </c>
-      <c r="AM5" s="27" t="inlineStr">
+      <c r="AN5" s="27" t="inlineStr">
         <is>
           <t>Cash discount percentage</t>
         </is>
       </c>
-      <c r="AN5" s="27" t="inlineStr">
+      <c r="AO5" s="27" t="inlineStr">
         <is>
           <t>Cash discount amount 3</t>
         </is>
       </c>
-      <c r="AO5" s="27" t="inlineStr">
+      <c r="AP5" s="27" t="inlineStr">
         <is>
           <t>Payment method - accounts payable</t>
         </is>
       </c>
-      <c r="AP5" s="27" t="inlineStr">
+      <c r="AQ5" s="27" t="inlineStr">
         <is>
           <t>Payment terms</t>
         </is>
       </c>
-      <c r="AQ5" s="27" t="inlineStr">
+      <c r="AR5" s="27" t="inlineStr">
         <is>
           <t>Exchange rate</t>
         </is>
       </c>
-      <c r="AR5" s="27" t="inlineStr">
+      <c r="AS5" s="27" t="inlineStr">
         <is>
           <t>Exchange rate type</t>
         </is>
       </c>
-      <c r="AS5" s="27" t="inlineStr">
+      <c r="AT5" s="27" t="inlineStr">
         <is>
           <t>Order date</t>
         </is>
       </c>
-      <c r="AT5" s="27" t="inlineStr">
+      <c r="AU5" s="27" t="inlineStr">
         <is>
           <t>Delivery date</t>
         </is>
       </c>
-      <c r="AU5" s="27" t="inlineStr">
+      <c r="AV5" s="27" t="inlineStr">
         <is>
           <t>Future rate agreement number</t>
         </is>
       </c>
-      <c r="AV5" s="27" t="inlineStr">
+      <c r="AW5" s="27" t="inlineStr">
         <is>
           <t>Service code</t>
         </is>
       </c>
-      <c r="AW5" s="27" t="inlineStr">
+      <c r="AX5" s="27" t="inlineStr">
         <is>
           <t>Voucher number series</t>
         </is>
       </c>
-      <c r="AX5" s="27" t="inlineStr">
+      <c r="AY5" s="27" t="inlineStr">
         <is>
           <t>Voucher number</t>
         </is>
       </c>
-      <c r="AY5" s="27" t="inlineStr">
+      <c r="AZ5" s="27" t="inlineStr">
         <is>
           <t>Accounting date</t>
         </is>
       </c>
-      <c r="AZ5" s="27" t="inlineStr">
+      <c r="BA5" s="27" t="inlineStr">
         <is>
           <t>Invoice per receiving number</t>
         </is>
       </c>
-      <c r="BA5" s="27" t="inlineStr">
+      <c r="BB5" s="27" t="inlineStr">
         <is>
           <t>Supplier acceptance</t>
         </is>
       </c>
-      <c r="BB5" s="27" t="inlineStr">
+      <c r="BC5" s="27" t="inlineStr">
         <is>
           <t>Conditions for adding lines</t>
         </is>
       </c>
-      <c r="BC5" s="27" t="inlineStr">
+      <c r="BD5" s="27" t="inlineStr">
         <is>
           <t>Our invoicing address</t>
         </is>
       </c>
-      <c r="BD5" s="27" t="inlineStr">
+      <c r="BE5" s="27" t="inlineStr">
         <is>
           <t>Authorized user</t>
         </is>
       </c>
-      <c r="BE5" s="27" t="inlineStr">
+      <c r="BF5" s="27" t="inlineStr">
         <is>
           <t>AP standard document</t>
         </is>
       </c>
-      <c r="BF5" s="27" t="inlineStr">
+      <c r="BG5" s="27" t="inlineStr">
         <is>
           <t>Debit note reason</t>
         </is>
       </c>
-      <c r="BG5" s="27" t="inlineStr">
+      <c r="BH5" s="27" t="inlineStr">
         <is>
           <t>Text line 1</t>
         </is>
       </c>
-      <c r="BH5" s="27" t="inlineStr">
+      <c r="BI5" s="27" t="inlineStr">
         <is>
           <t>Text line 2</t>
         </is>
       </c>
-      <c r="BI5" s="27" t="inlineStr">
+      <c r="BJ5" s="27" t="inlineStr">
         <is>
           <t>Text line 3</t>
         </is>
       </c>
-      <c r="BJ5" s="27" t="inlineStr">
+      <c r="BK5" s="27" t="inlineStr">
         <is>
           <t>Base country</t>
         </is>
       </c>
-      <c r="BK5" s="27" t="inlineStr">
+      <c r="BL5" s="27" t="inlineStr">
         <is>
           <t>From/To country</t>
         </is>
       </c>
-      <c r="BL5" s="27" t="inlineStr">
+      <c r="BM5" s="27" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="BM5" s="27" t="inlineStr">
+      <c r="BN5" s="27" t="inlineStr">
         <is>
           <t>Trade code</t>
         </is>
       </c>
-      <c r="BN5" s="27" t="inlineStr">
+      <c r="BO5" s="27" t="inlineStr">
         <is>
           <t>Tax applicable</t>
         </is>
       </c>
-      <c r="BO5" s="27" t="inlineStr">
+      <c r="BP5" s="27" t="inlineStr">
         <is>
           <t>Purchase order number</t>
         </is>
       </c>
-      <c r="BP5" s="27" t="inlineStr">
+      <c r="BQ5" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="BQ5" s="27" t="inlineStr">
+      <c r="BR5" s="27" t="inlineStr">
         <is>
           <t>Job number</t>
         </is>
       </c>
-      <c r="BR5" s="27" t="inlineStr">
+      <c r="BS5" s="27" t="inlineStr">
         <is>
           <t>Job name</t>
         </is>
       </c>
-      <c r="BS5" s="27" t="inlineStr">
+      <c r="BT5" s="27" t="inlineStr">
         <is>
           <t>Rejection reason</t>
         </is>
       </c>
-      <c r="BT5" s="27" t="inlineStr">
+      <c r="BU5" s="27" t="inlineStr">
         <is>
           <t>Rejection date</t>
         </is>
       </c>
-      <c r="BU5" s="27" t="inlineStr">
+      <c r="BV5" s="27" t="inlineStr">
         <is>
           <t>Reprint after adjustment</t>
         </is>
       </c>
-      <c r="BV5" s="27" t="inlineStr">
+      <c r="BW5" s="27" t="inlineStr">
         <is>
           <t>Approval date</t>
         </is>
       </c>
-      <c r="BW5" s="27" t="inlineStr">
+      <c r="BX5" s="27" t="inlineStr">
         <is>
           <t>Adjusted amount</t>
         </is>
       </c>
-      <c r="BX5" s="27" t="inlineStr">
+      <c r="BY5" s="27" t="inlineStr">
         <is>
           <t>Credit number</t>
         </is>
       </c>
-      <c r="BY5" s="27" t="inlineStr">
+      <c r="BZ5" s="27" t="inlineStr">
         <is>
           <t>Your reference</t>
         </is>
       </c>
-      <c r="BZ5" s="27" t="inlineStr">
+      <c r="CA5" s="27" t="inlineStr">
         <is>
           <t>Data identity</t>
         </is>
       </c>
-      <c r="CA5" s="27" t="inlineStr">
+      <c r="CB5" s="27" t="inlineStr">
         <is>
           <t>Original invoice number</t>
         </is>
       </c>
-      <c r="CB5" s="27" t="inlineStr">
+      <c r="CC5" s="27" t="inlineStr">
         <is>
           <t>Original year</t>
         </is>
       </c>
-      <c r="CC5" s="27" t="inlineStr">
+      <c r="CD5" s="27" t="inlineStr">
         <is>
           <t>Reference number</t>
         </is>
       </c>
-      <c r="CD5" s="27" t="inlineStr">
+      <c r="CE5" s="27" t="inlineStr">
         <is>
           <t>Payment request number</t>
         </is>
       </c>
-      <c r="CE5" s="27" t="inlineStr">
+      <c r="CF5" s="27" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="CF5" s="27" t="inlineStr">
+      <c r="CG5" s="27" t="inlineStr">
         <is>
           <t>Bank account identity</t>
         </is>
       </c>
-      <c r="CG5" s="27" t="inlineStr">
+      <c r="CH5" s="27" t="inlineStr">
         <is>
           <t>Geographical code</t>
         </is>
       </c>
-      <c r="CH5" s="27" t="inlineStr">
+      <c r="CI5" s="27" t="inlineStr">
         <is>
           <t>Tax included</t>
         </is>
       </c>
-      <c r="CI5" s="27" t="inlineStr">
+      <c r="CJ5" s="27" t="inlineStr">
         <is>
           <t>Standard point location code</t>
         </is>
       </c>
-      <c r="CJ5" s="27" t="inlineStr">
+      <c r="CK5" s="27" t="inlineStr">
         <is>
           <t>Invoice aggregation key 1</t>
         </is>
       </c>
-      <c r="CK5" s="27" t="inlineStr">
+      <c r="CL5" s="27" t="inlineStr">
         <is>
           <t>Invoice aggregation key 2</t>
         </is>
       </c>
-      <c r="CL5" s="27" t="inlineStr">
+      <c r="CM5" s="27" t="inlineStr">
         <is>
           <t>Invoice aggregation key 3</t>
         </is>
       </c>
-      <c r="CM5" s="27" t="inlineStr">
+      <c r="CN5" s="27" t="inlineStr">
         <is>
           <t>Invoice aggregation key 4</t>
         </is>
       </c>
-      <c r="CN5" s="27" t="inlineStr">
+      <c r="CO5" s="27" t="inlineStr">
         <is>
           <t>Invoice aggregation key 5</t>
         </is>
       </c>
-      <c r="CO5" s="27" t="inlineStr">
+      <c r="CP5" s="27" t="inlineStr">
         <is>
           <t>Correlation ID</t>
         </is>
       </c>
-      <c r="CP5" s="27" t="inlineStr">
+      <c r="CQ5" s="27" t="inlineStr">
         <is>
           <t>Cash discount default values</t>
         </is>
       </c>
-      <c r="CQ5" s="27" t="inlineStr">
+      <c r="CR5" s="27" t="inlineStr">
         <is>
           <t>Finance reason code</t>
         </is>
       </c>
-      <c r="CR5" s="27" t="inlineStr">
+      <c r="CS5" s="27" t="inlineStr">
         <is>
           <t>Parallel invoice number</t>
         </is>
       </c>
-      <c r="CS5" s="27" t="inlineStr">
+      <c r="CT5" s="27" t="inlineStr">
         <is>
           <t>Credit request reference</t>
         </is>
       </c>
-      <c r="CT5" s="27" t="inlineStr">
+      <c r="CU5" s="27" t="inlineStr">
         <is>
           <t>Credit request year</t>
         </is>
       </c>
-      <c r="CU5" s="27" t="inlineStr">
+      <c r="CV5" s="27" t="inlineStr">
         <is>
           <t>Credit request transaction type</t>
         </is>
       </c>
-      <c r="CV5" s="27" t="inlineStr">
+      <c r="CW5" s="27" t="inlineStr">
         <is>
           <t>VAT on expense report</t>
         </is>
       </c>
-      <c r="CW5" s="27" t="inlineStr">
+      <c r="CX5" s="27" t="inlineStr">
         <is>
           <t>External reference number</t>
         </is>
       </c>
-      <c r="CX5" s="27" t="inlineStr">
+      <c r="CY5" s="27" t="inlineStr">
         <is>
           <t>Financial agreement ID</t>
         </is>
       </c>
-      <c r="CY5" s="27" t="inlineStr">
+      <c r="CZ5" s="27" t="inlineStr">
         <is>
           <t>User-defined accounting control object</t>
         </is>
       </c>
-      <c r="CZ5" s="27" t="inlineStr">
+      <c r="DA5" s="27" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="DA5" s="27" t="inlineStr">
+      <c r="DB5" s="27" t="inlineStr">
         <is>
           <t>Voucher number series</t>
         </is>
       </c>
-      <c r="DB5" s="27" t="inlineStr">
+      <c r="DC5" s="27" t="inlineStr">
         <is>
           <t>Delivery note number</t>
         </is>
       </c>
-      <c r="DC5" s="27" t="inlineStr">
+      <c r="DD5" s="27" t="inlineStr">
         <is>
           <t>Supplier rebate agreement number</t>
         </is>
       </c>
-      <c r="DD5" s="27" t="inlineStr">
+      <c r="DE5" s="27" t="inlineStr">
         <is>
           <t>VAT bank account identity</t>
         </is>
       </c>
-      <c r="DE5" s="27" t="inlineStr">
+      <c r="DF5" s="27" t="inlineStr">
         <is>
           <t>Our reference - invoice</t>
         </is>
       </c>
-      <c r="DF5" s="27" t="inlineStr">
+      <c r="DG5" s="27" t="inlineStr">
         <is>
           <t>Self-billing correction method</t>
         </is>
       </c>
-      <c r="DG5" s="27" t="inlineStr">
+      <c r="DH5" s="27" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="DH5" s="27" t="inlineStr">
+      <c r="DI5" s="27" t="inlineStr">
         <is>
           <t>Self-billing invoice number</t>
         </is>
       </c>
-      <c r="DI5" s="27" t="inlineStr">
+      <c r="DJ5" s="27" t="inlineStr">
         <is>
           <t>Self-billing credit invoice number</t>
         </is>
       </c>
-      <c r="DJ5" s="27" t="inlineStr">
+      <c r="DK5" s="27" t="inlineStr">
         <is>
           <t>Self-billing original invoice</t>
         </is>
       </c>
-      <c r="DK5" s="27" t="inlineStr">
+      <c r="DL5" s="27" t="inlineStr">
         <is>
           <t>Withholding tax applied on inv amount</t>
+        </is>
+      </c>
+      <c r="DM5" s="27" t="inlineStr">
+        <is>
+          <t>Batch invoice manual validation status</t>
+        </is>
+      </c>
+      <c r="DN5" s="27" t="inlineStr">
+        <is>
+          <t>Invoice batch document type code</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>INBN</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>SPYN</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>SUNO</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>SINO</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>IBHE</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>IBLE</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>BIST</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>PRNT</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>IBTP</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>SUPA</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="L6" s="28" t="inlineStr">
         <is>
           <t>MSID</t>
         </is>
       </c>
-      <c r="L6" s="28" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t>MSGD</t>
         </is>
       </c>
-      <c r="M6" s="28" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>IMCD</t>
         </is>
       </c>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t>ENME</t>
         </is>
       </c>
-      <c r="O6" s="28" t="inlineStr">
+      <c r="P6" s="28" t="inlineStr">
         <is>
           <t>EALS</t>
         </is>
       </c>
-      <c r="P6" s="28" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t>VRNO</t>
         </is>
       </c>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="R6" s="28" t="inlineStr">
         <is>
           <t>EALP</t>
         </is>
       </c>
-      <c r="R6" s="28" t="inlineStr">
+      <c r="S6" s="28" t="inlineStr">
         <is>
           <t>EALR</t>
         </is>
       </c>
-      <c r="S6" s="28" t="inlineStr">
+      <c r="T6" s="28" t="inlineStr">
         <is>
           <t>IVDT</t>
         </is>
       </c>
-      <c r="T6" s="28" t="inlineStr">
+      <c r="U6" s="28" t="inlineStr">
         <is>
           <t>DUDT</t>
         </is>
       </c>
-      <c r="U6" s="28" t="inlineStr">
+      <c r="V6" s="28" t="inlineStr">
         <is>
           <t>DNCO</t>
         </is>
       </c>
-      <c r="V6" s="28" t="inlineStr">
+      <c r="W6" s="28" t="inlineStr">
         <is>
           <t>VTAM</t>
         </is>
       </c>
-      <c r="W6" s="28" t="inlineStr">
+      <c r="X6" s="28" t="inlineStr">
         <is>
           <t>CUCD</t>
         </is>
       </c>
-      <c r="X6" s="28" t="inlineStr">
+      <c r="Y6" s="28" t="inlineStr">
         <is>
           <t>CUAM</t>
         </is>
       </c>
-      <c r="Y6" s="28" t="inlineStr">
+      <c r="Z6" s="28" t="inlineStr">
         <is>
           <t>TLNA</t>
         </is>
       </c>
-      <c r="Z6" s="28" t="inlineStr">
+      <c r="AA6" s="28" t="inlineStr">
         <is>
           <t>TASD</t>
         </is>
       </c>
-      <c r="AA6" s="28" t="inlineStr">
+      <c r="AB6" s="28" t="inlineStr">
         <is>
           <t>TTXA</t>
         </is>
       </c>
-      <c r="AB6" s="28" t="inlineStr">
+      <c r="AC6" s="28" t="inlineStr">
         <is>
           <t>TCHG</t>
         </is>
       </c>
-      <c r="AC6" s="28" t="inlineStr">
+      <c r="AD6" s="28" t="inlineStr">
         <is>
           <t>TOPA</t>
         </is>
       </c>
-      <c r="AD6" s="28" t="inlineStr">
+      <c r="AE6" s="28" t="inlineStr">
         <is>
           <t>PRPA</t>
         </is>
       </c>
-      <c r="AE6" s="28" t="inlineStr">
+      <c r="AF6" s="28" t="inlineStr">
         <is>
           <t>TECD</t>
         </is>
       </c>
-      <c r="AF6" s="28" t="inlineStr">
+      <c r="AG6" s="28" t="inlineStr">
         <is>
           <t>CDT1</t>
         </is>
       </c>
-      <c r="AG6" s="28" t="inlineStr">
+      <c r="AH6" s="28" t="inlineStr">
         <is>
           <t>CDP1</t>
         </is>
       </c>
-      <c r="AH6" s="28" t="inlineStr">
+      <c r="AI6" s="28" t="inlineStr">
         <is>
           <t>CDC1</t>
         </is>
       </c>
-      <c r="AI6" s="28" t="inlineStr">
+      <c r="AJ6" s="28" t="inlineStr">
         <is>
           <t>CDT2</t>
         </is>
       </c>
-      <c r="AJ6" s="28" t="inlineStr">
+      <c r="AK6" s="28" t="inlineStr">
         <is>
           <t>CDP2</t>
         </is>
       </c>
-      <c r="AK6" s="28" t="inlineStr">
+      <c r="AL6" s="28" t="inlineStr">
         <is>
           <t>CDC2</t>
         </is>
       </c>
-      <c r="AL6" s="28" t="inlineStr">
+      <c r="AM6" s="28" t="inlineStr">
         <is>
           <t>CDT3</t>
         </is>
       </c>
-      <c r="AM6" s="28" t="inlineStr">
+      <c r="AN6" s="28" t="inlineStr">
         <is>
           <t>CDP3</t>
         </is>
       </c>
-      <c r="AN6" s="28" t="inlineStr">
+      <c r="AO6" s="28" t="inlineStr">
         <is>
           <t>CDC3</t>
         </is>
       </c>
-      <c r="AO6" s="28" t="inlineStr">
+      <c r="AP6" s="28" t="inlineStr">
         <is>
           <t>PYME</t>
         </is>
       </c>
-      <c r="AP6" s="28" t="inlineStr">
+      <c r="AQ6" s="28" t="inlineStr">
         <is>
           <t>TEPY</t>
         </is>
       </c>
-      <c r="AQ6" s="28" t="inlineStr">
+      <c r="AR6" s="28" t="inlineStr">
         <is>
           <t>ARAT</t>
         </is>
       </c>
-      <c r="AR6" s="28" t="inlineStr">
+      <c r="AS6" s="28" t="inlineStr">
         <is>
           <t>CRTP</t>
         </is>
       </c>
-      <c r="AS6" s="28" t="inlineStr">
+      <c r="AT6" s="28" t="inlineStr">
         <is>
           <t>PUDT</t>
         </is>
       </c>
-      <c r="AT6" s="28" t="inlineStr">
+      <c r="AU6" s="28" t="inlineStr">
         <is>
           <t>DEDA</t>
         </is>
       </c>
-      <c r="AU6" s="28" t="inlineStr">
+      <c r="AV6" s="28" t="inlineStr">
         <is>
           <t>FECN</t>
         </is>
       </c>
-      <c r="AV6" s="28" t="inlineStr">
+      <c r="AW6" s="28" t="inlineStr">
         <is>
           <t>SERS</t>
         </is>
       </c>
-      <c r="AW6" s="28" t="inlineStr">
+      <c r="AX6" s="28" t="inlineStr">
         <is>
           <t>VSER</t>
         </is>
       </c>
-      <c r="AX6" s="28" t="inlineStr">
+      <c r="AY6" s="28" t="inlineStr">
         <is>
           <t>VONO</t>
         </is>
       </c>
-      <c r="AY6" s="28" t="inlineStr">
+      <c r="AZ6" s="28" t="inlineStr">
         <is>
           <t>ACDT</t>
         </is>
       </c>
-      <c r="AZ6" s="28" t="inlineStr">
+      <c r="BA6" s="28" t="inlineStr">
         <is>
           <t>UPBI</t>
         </is>
       </c>
-      <c r="BA6" s="28" t="inlineStr">
+      <c r="BB6" s="28" t="inlineStr">
         <is>
           <t>SUAC</t>
         </is>
       </c>
-      <c r="BB6" s="28" t="inlineStr">
+      <c r="BC6" s="28" t="inlineStr">
         <is>
           <t>SBAD</t>
         </is>
       </c>
-      <c r="BC6" s="28" t="inlineStr">
+      <c r="BD6" s="28" t="inlineStr">
         <is>
           <t>PYAD</t>
         </is>
       </c>
-      <c r="BD6" s="28" t="inlineStr">
+      <c r="BE6" s="28" t="inlineStr">
         <is>
           <t>APCD</t>
         </is>
       </c>
-      <c r="BE6" s="28" t="inlineStr">
+      <c r="BF6" s="28" t="inlineStr">
         <is>
           <t>SDAP</t>
         </is>
       </c>
-      <c r="BF6" s="28" t="inlineStr">
+      <c r="BG6" s="28" t="inlineStr">
         <is>
           <t>DNRE</t>
         </is>
       </c>
-      <c r="BG6" s="28" t="inlineStr">
+      <c r="BH6" s="28" t="inlineStr">
         <is>
           <t>SDA1</t>
         </is>
       </c>
-      <c r="BH6" s="28" t="inlineStr">
+      <c r="BI6" s="28" t="inlineStr">
         <is>
           <t>SDA2</t>
         </is>
       </c>
-      <c r="BI6" s="28" t="inlineStr">
+      <c r="BJ6" s="28" t="inlineStr">
         <is>
           <t>SDA3</t>
         </is>
       </c>
-      <c r="BJ6" s="28" t="inlineStr">
+      <c r="BK6" s="28" t="inlineStr">
         <is>
           <t>BSCD</t>
         </is>
       </c>
-      <c r="BK6" s="28" t="inlineStr">
+      <c r="BL6" s="28" t="inlineStr">
         <is>
           <t>FTCO</t>
         </is>
       </c>
-      <c r="BL6" s="28" t="inlineStr">
+      <c r="BM6" s="28" t="inlineStr">
         <is>
           <t>ECAR</t>
         </is>
       </c>
-      <c r="BM6" s="28" t="inlineStr">
+      <c r="BN6" s="28" t="inlineStr">
         <is>
           <t>TDCD</t>
         </is>
       </c>
-      <c r="BN6" s="28" t="inlineStr">
+      <c r="BO6" s="28" t="inlineStr">
         <is>
           <t>TXAP</t>
         </is>
       </c>
-      <c r="BO6" s="28" t="inlineStr">
+      <c r="BP6" s="28" t="inlineStr">
         <is>
           <t>PUNO</t>
         </is>
       </c>
-      <c r="BP6" s="28" t="inlineStr">
+      <c r="BQ6" s="28" t="inlineStr">
         <is>
           <t>APCT</t>
         </is>
       </c>
-      <c r="BQ6" s="28" t="inlineStr">
+      <c r="BR6" s="28" t="inlineStr">
         <is>
           <t>JNU</t>
         </is>
       </c>
-      <c r="BR6" s="28" t="inlineStr">
+      <c r="BS6" s="28" t="inlineStr">
         <is>
           <t>JNA</t>
         </is>
       </c>
-      <c r="BS6" s="28" t="inlineStr">
+      <c r="BT6" s="28" t="inlineStr">
         <is>
           <t>SCRE</t>
         </is>
       </c>
-      <c r="BT6" s="28" t="inlineStr">
+      <c r="BU6" s="28" t="inlineStr">
         <is>
           <t>REJD</t>
         </is>
       </c>
-      <c r="BU6" s="28" t="inlineStr">
+      <c r="BV6" s="28" t="inlineStr">
         <is>
           <t>RPAA</t>
         </is>
       </c>
-      <c r="BV6" s="28" t="inlineStr">
+      <c r="BW6" s="28" t="inlineStr">
         <is>
           <t>AAPD</t>
         </is>
       </c>
-      <c r="BW6" s="28" t="inlineStr">
+      <c r="BX6" s="28" t="inlineStr">
         <is>
           <t>ADAB</t>
         </is>
       </c>
-      <c r="BX6" s="28" t="inlineStr">
+      <c r="BY6" s="28" t="inlineStr">
         <is>
           <t>CRNO</t>
         </is>
       </c>
-      <c r="BY6" s="28" t="inlineStr">
+      <c r="BZ6" s="28" t="inlineStr">
         <is>
           <t>YRE1</t>
         </is>
       </c>
-      <c r="BZ6" s="28" t="inlineStr">
+      <c r="CA6" s="28" t="inlineStr">
         <is>
           <t>DTID</t>
         </is>
       </c>
-      <c r="CA6" s="28" t="inlineStr">
+      <c r="CB6" s="28" t="inlineStr">
         <is>
           <t>DNOI</t>
         </is>
       </c>
-      <c r="CB6" s="28" t="inlineStr">
+      <c r="CC6" s="28" t="inlineStr">
         <is>
           <t>OYEA</t>
         </is>
       </c>
-      <c r="CC6" s="28" t="inlineStr">
+      <c r="CD6" s="28" t="inlineStr">
         <is>
           <t>PPYR</t>
         </is>
       </c>
-      <c r="CD6" s="28" t="inlineStr">
+      <c r="CE6" s="28" t="inlineStr">
         <is>
           <t>PPYN</t>
         </is>
       </c>
-      <c r="CE6" s="28" t="inlineStr">
+      <c r="CF6" s="28" t="inlineStr">
         <is>
           <t>YEA4</t>
         </is>
       </c>
-      <c r="CF6" s="28" t="inlineStr">
+      <c r="CG6" s="28" t="inlineStr">
         <is>
           <t>BKID</t>
         </is>
       </c>
-      <c r="CG6" s="28" t="inlineStr">
+      <c r="CH6" s="28" t="inlineStr">
         <is>
           <t>GEOC</t>
         </is>
       </c>
-      <c r="CH6" s="28" t="inlineStr">
+      <c r="CI6" s="28" t="inlineStr">
         <is>
           <t>TXIN</t>
         </is>
       </c>
-      <c r="CI6" s="28" t="inlineStr">
+      <c r="CJ6" s="28" t="inlineStr">
         <is>
           <t>SPLE</t>
         </is>
       </c>
-      <c r="CJ6" s="28" t="inlineStr">
+      <c r="CK6" s="28" t="inlineStr">
         <is>
           <t>IAK1</t>
         </is>
       </c>
-      <c r="CK6" s="28" t="inlineStr">
+      <c r="CL6" s="28" t="inlineStr">
         <is>
           <t>IAK2</t>
         </is>
       </c>
-      <c r="CL6" s="28" t="inlineStr">
+      <c r="CM6" s="28" t="inlineStr">
         <is>
           <t>IAK3</t>
         </is>
       </c>
-      <c r="CM6" s="28" t="inlineStr">
+      <c r="CN6" s="28" t="inlineStr">
         <is>
           <t>IAK4</t>
         </is>
       </c>
-      <c r="CN6" s="28" t="inlineStr">
+      <c r="CO6" s="28" t="inlineStr">
         <is>
           <t>IAK5</t>
         </is>
       </c>
-      <c r="CO6" s="28" t="inlineStr">
+      <c r="CP6" s="28" t="inlineStr">
         <is>
           <t>CORI</t>
         </is>
       </c>
-      <c r="CP6" s="28" t="inlineStr">
+      <c r="CQ6" s="28" t="inlineStr">
         <is>
           <t>CDDV</t>
         </is>
       </c>
-      <c r="CQ6" s="28" t="inlineStr">
+      <c r="CR6" s="28" t="inlineStr">
         <is>
           <t>FRSC</t>
         </is>
       </c>
-      <c r="CR6" s="28" t="inlineStr">
+      <c r="CS6" s="28" t="inlineStr">
         <is>
           <t>PAIN</t>
         </is>
       </c>
-      <c r="CS6" s="28" t="inlineStr">
+      <c r="CT6" s="28" t="inlineStr">
         <is>
           <t>CRRR</t>
         </is>
       </c>
-      <c r="CT6" s="28" t="inlineStr">
+      <c r="CU6" s="28" t="inlineStr">
         <is>
           <t>CRYE</t>
         </is>
       </c>
-      <c r="CU6" s="28" t="inlineStr">
+      <c r="CV6" s="28" t="inlineStr">
         <is>
           <t>CTTP</t>
         </is>
       </c>
-      <c r="CV6" s="28" t="inlineStr">
+      <c r="CW6" s="28" t="inlineStr">
         <is>
           <t>EXRP</t>
         </is>
       </c>
-      <c r="CW6" s="28" t="inlineStr">
+      <c r="CX6" s="28" t="inlineStr">
         <is>
           <t>EORN</t>
         </is>
       </c>
-      <c r="CX6" s="28" t="inlineStr">
+      <c r="CY6" s="28" t="inlineStr">
         <is>
           <t>FAGN</t>
         </is>
       </c>
-      <c r="CY6" s="28" t="inlineStr">
+      <c r="CZ6" s="28" t="inlineStr">
         <is>
           <t>ACRF</t>
         </is>
       </c>
-      <c r="CZ6" s="28" t="inlineStr">
+      <c r="DA6" s="28" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="DA6" s="28" t="inlineStr">
+      <c r="DB6" s="28" t="inlineStr">
         <is>
           <t>VSE2</t>
         </is>
       </c>
-      <c r="DB6" s="28" t="inlineStr">
+      <c r="DC6" s="28" t="inlineStr">
         <is>
           <t>SUDO</t>
         </is>
       </c>
-      <c r="DC6" s="28" t="inlineStr">
+      <c r="DD6" s="28" t="inlineStr">
         <is>
           <t>SRAG</t>
         </is>
       </c>
-      <c r="DD6" s="28" t="inlineStr">
+      <c r="DE6" s="28" t="inlineStr">
         <is>
           <t>BKIS</t>
         </is>
       </c>
-      <c r="DE6" s="28" t="inlineStr">
+      <c r="DF6" s="28" t="inlineStr">
         <is>
           <t>OURF</t>
         </is>
       </c>
-      <c r="DF6" s="28" t="inlineStr">
+      <c r="DG6" s="28" t="inlineStr">
         <is>
           <t>SBCM</t>
         </is>
       </c>
-      <c r="DG6" s="28" t="inlineStr">
+      <c r="DH6" s="28" t="inlineStr">
         <is>
           <t>FACI</t>
         </is>
       </c>
-      <c r="DH6" s="28" t="inlineStr">
+      <c r="DI6" s="28" t="inlineStr">
         <is>
           <t>SBSI</t>
         </is>
       </c>
-      <c r="DI6" s="28" t="inlineStr">
+      <c r="DJ6" s="28" t="inlineStr">
         <is>
           <t>SBCI</t>
         </is>
       </c>
-      <c r="DJ6" s="28" t="inlineStr">
+      <c r="DK6" s="28" t="inlineStr">
         <is>
           <t>SBOI</t>
         </is>
       </c>
-      <c r="DK6" s="28" t="inlineStr">
+      <c r="DL6" s="28" t="inlineStr">
         <is>
           <t>WHAI</t>
+        </is>
+      </c>
+      <c r="DM6" s="28" t="inlineStr">
+        <is>
+          <t>BIVS</t>
+        </is>
+      </c>
+      <c r="DN6" s="28" t="inlineStr">
+        <is>
+          <t>IBDT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="L7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N7" s="29" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O7" s="29" t="inlineStr">
+      <c r="P7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P7" s="29" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q7" s="29" t="inlineStr">
+      <c r="R7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="R7" s="29" t="inlineStr">
+      <c r="S7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S7" s="29" t="inlineStr">
+      <c r="T7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="T7" s="29" t="inlineStr">
+      <c r="U7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U7" s="29" t="inlineStr">
+      <c r="V7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="V7" s="29" t="inlineStr">
+      <c r="W7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W7" s="29" t="inlineStr">
+      <c r="X7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="X7" s="29" t="inlineStr">
+      <c r="Y7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Y7" s="29" t="inlineStr">
+      <c r="Z7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Z7" s="29" t="inlineStr">
+      <c r="AA7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA7" s="29" t="inlineStr">
+      <c r="AB7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AB7" s="29" t="inlineStr">
+      <c r="AC7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AC7" s="29" t="inlineStr">
+      <c r="AD7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AD7" s="29" t="inlineStr">
+      <c r="AE7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AE7" s="29" t="inlineStr">
+      <c r="AF7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AF7" s="29" t="inlineStr">
+      <c r="AG7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AG7" s="29" t="inlineStr">
+      <c r="AH7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AH7" s="29" t="inlineStr">
+      <c r="AI7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AI7" s="29" t="inlineStr">
+      <c r="AJ7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AJ7" s="29" t="inlineStr">
+      <c r="AK7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AK7" s="29" t="inlineStr">
+      <c r="AL7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AL7" s="29" t="inlineStr">
+      <c r="AM7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AM7" s="29" t="inlineStr">
+      <c r="AN7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AN7" s="29" t="inlineStr">
+      <c r="AO7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AO7" s="29" t="inlineStr">
+      <c r="AP7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AP7" s="29" t="inlineStr">
+      <c r="AQ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AQ7" s="29" t="inlineStr">
+      <c r="AR7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AR7" s="29" t="inlineStr">
+      <c r="AS7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AS7" s="29" t="inlineStr">
+      <c r="AT7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AT7" s="29" t="inlineStr">
+      <c r="AU7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AU7" s="29" t="inlineStr">
+      <c r="AV7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AV7" s="29" t="inlineStr">
+      <c r="AW7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AW7" s="29" t="inlineStr">
+      <c r="AX7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AX7" s="29" t="inlineStr">
+      <c r="AY7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AY7" s="29" t="inlineStr">
+      <c r="AZ7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AZ7" s="29" t="inlineStr">
+      <c r="BA7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BA7" s="29" t="inlineStr">
+      <c r="BB7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BB7" s="29" t="inlineStr">
+      <c r="BC7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BC7" s="29" t="inlineStr">
+      <c r="BD7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BD7" s="29" t="inlineStr">
+      <c r="BE7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BE7" s="29" t="inlineStr">
+      <c r="BF7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BF7" s="29" t="inlineStr">
+      <c r="BG7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BG7" s="29" t="inlineStr">
+      <c r="BH7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BH7" s="29" t="inlineStr">
+      <c r="BI7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BI7" s="29" t="inlineStr">
+      <c r="BJ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BJ7" s="29" t="inlineStr">
+      <c r="BK7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BK7" s="29" t="inlineStr">
+      <c r="BL7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BL7" s="29" t="inlineStr">
+      <c r="BM7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BM7" s="29" t="inlineStr">
+      <c r="BN7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BN7" s="29" t="inlineStr">
+      <c r="BO7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BO7" s="29" t="inlineStr">
+      <c r="BP7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BP7" s="29" t="inlineStr">
+      <c r="BQ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BQ7" s="29" t="inlineStr">
+      <c r="BR7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BR7" s="29" t="inlineStr">
+      <c r="BS7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BS7" s="29" t="inlineStr">
+      <c r="BT7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BT7" s="29" t="inlineStr">
+      <c r="BU7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BU7" s="29" t="inlineStr">
+      <c r="BV7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BV7" s="29" t="inlineStr">
+      <c r="BW7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BW7" s="29" t="inlineStr">
+      <c r="BX7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BX7" s="29" t="inlineStr">
+      <c r="BY7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BY7" s="29" t="inlineStr">
+      <c r="BZ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BZ7" s="29" t="inlineStr">
+      <c r="CA7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CA7" s="29" t="inlineStr">
+      <c r="CB7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CB7" s="29" t="inlineStr">
+      <c r="CC7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CC7" s="29" t="inlineStr">
+      <c r="CD7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CD7" s="29" t="inlineStr">
+      <c r="CE7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CE7" s="29" t="inlineStr">
+      <c r="CF7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CF7" s="29" t="inlineStr">
+      <c r="CG7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CG7" s="29" t="inlineStr">
+      <c r="CH7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CH7" s="29" t="inlineStr">
+      <c r="CI7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CI7" s="29" t="inlineStr">
+      <c r="CJ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CJ7" s="29" t="inlineStr">
+      <c r="CK7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CK7" s="29" t="inlineStr">
+      <c r="CL7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CL7" s="29" t="inlineStr">
+      <c r="CM7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CM7" s="29" t="inlineStr">
+      <c r="CN7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CN7" s="29" t="inlineStr">
+      <c r="CO7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CO7" s="29" t="inlineStr">
+      <c r="CP7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CP7" s="29" t="inlineStr">
+      <c r="CQ7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CQ7" s="29" t="inlineStr">
+      <c r="CR7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CR7" s="29" t="inlineStr">
+      <c r="CS7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CS7" s="29" t="inlineStr">
+      <c r="CT7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CT7" s="29" t="inlineStr">
+      <c r="CU7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CU7" s="29" t="inlineStr">
+      <c r="CV7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CV7" s="29" t="inlineStr">
+      <c r="CW7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="CW7" s="29" t="inlineStr">
+      <c r="CX7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CX7" s="29" t="inlineStr">
+      <c r="CY7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CY7" s="29" t="inlineStr">
+      <c r="CZ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="CZ7" s="29" t="inlineStr">
+      <c r="DA7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="DA7" s="29" t="inlineStr">
+      <c r="DB7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DB7" s="29" t="inlineStr">
+      <c r="DC7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DC7" s="29" t="inlineStr">
+      <c r="DD7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DD7" s="29" t="inlineStr">
+      <c r="DE7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DE7" s="29" t="inlineStr">
+      <c r="DF7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DF7" s="29" t="inlineStr">
+      <c r="DG7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="DG7" s="29" t="inlineStr">
+      <c r="DH7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DH7" s="29" t="inlineStr">
+      <c r="DI7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DI7" s="29" t="inlineStr">
+      <c r="DJ7" s="29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="DJ7" s="29" t="inlineStr">
+      <c r="DK7" s="29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="DK7" s="29" t="inlineStr">
+      <c r="DL7" s="29" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="DM7" s="29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="DN7" s="29" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
+      <c r="M8" s="30" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="M8" s="30" t="inlineStr">
+      <c r="N8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N8" s="30" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O8" s="30" t="inlineStr">
+      <c r="P8" s="30" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="R8" s="30" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="S8" s="30" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="T8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T8" s="30" t="inlineStr">
+      <c r="U8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="U8" s="30" t="inlineStr">
+      <c r="V8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V8" s="30" t="inlineStr">
+      <c r="W8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="W8" s="30" t="inlineStr">
+      <c r="X8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X8" s="30" t="inlineStr">
+      <c r="Y8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Y8" s="30" t="inlineStr">
+      <c r="Z8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z8" s="30" t="inlineStr">
+      <c r="AA8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AA8" s="30" t="inlineStr">
+      <c r="AB8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AB8" s="30" t="inlineStr">
+      <c r="AC8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AC8" s="30" t="inlineStr">
+      <c r="AD8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AD8" s="30" t="inlineStr">
+      <c r="AE8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AE8" s="30" t="inlineStr">
+      <c r="AF8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AF8" s="30" t="inlineStr">
+      <c r="AG8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG8" s="30" t="inlineStr">
+      <c r="AH8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AH8" s="30" t="inlineStr">
+      <c r="AI8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI8" s="30" t="inlineStr">
+      <c r="AJ8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AJ8" s="30" t="inlineStr">
+      <c r="AK8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK8" s="30" t="inlineStr">
+      <c r="AL8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AL8" s="30" t="inlineStr">
+      <c r="AM8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AM8" s="30" t="inlineStr">
+      <c r="AN8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AN8" s="30" t="inlineStr">
+      <c r="AO8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AO8" s="30" t="inlineStr">
+      <c r="AP8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AP8" s="30" t="inlineStr">
+      <c r="AQ8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AQ8" s="30" t="inlineStr">
+      <c r="AR8" s="30" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AR8" s="30" t="inlineStr">
+      <c r="AS8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AS8" s="30" t="inlineStr">
+      <c r="AT8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AT8" s="30" t="inlineStr">
+      <c r="AU8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AU8" s="30" t="inlineStr">
+      <c r="AV8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AV8" s="30" t="inlineStr">
+      <c r="AW8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AW8" s="30" t="inlineStr">
+      <c r="AX8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AX8" s="30" t="inlineStr">
+      <c r="AY8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AY8" s="30" t="inlineStr">
+      <c r="AZ8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AZ8" s="30" t="inlineStr">
+      <c r="BA8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BA8" s="30" t="inlineStr">
+      <c r="BB8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BB8" s="30" t="inlineStr">
+      <c r="BC8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BC8" s="30" t="inlineStr">
+      <c r="BD8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BD8" s="30" t="inlineStr">
+      <c r="BE8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BE8" s="30" t="inlineStr">
+      <c r="BF8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BF8" s="30" t="inlineStr">
+      <c r="BG8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BG8" s="30" t="inlineStr">
+      <c r="BH8" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BH8" s="30" t="inlineStr">
+      <c r="BI8" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BI8" s="30" t="inlineStr">
+      <c r="BJ8" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BJ8" s="30" t="inlineStr">
+      <c r="BK8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BK8" s="30" t="inlineStr">
+      <c r="BL8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL8" s="30" t="inlineStr">
+      <c r="BM8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BM8" s="30" t="inlineStr">
+      <c r="BN8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BN8" s="30" t="inlineStr">
+      <c r="BO8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BO8" s="30" t="inlineStr">
+      <c r="BP8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BP8" s="30" t="inlineStr">
+      <c r="BQ8" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="BQ8" s="30" t="inlineStr">
+      <c r="BR8" s="30" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BR8" s="30" t="inlineStr">
+      <c r="BS8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BS8" s="30" t="inlineStr">
+      <c r="BT8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BT8" s="30" t="inlineStr">
+      <c r="BU8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BU8" s="30" t="inlineStr">
+      <c r="BV8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BV8" s="30" t="inlineStr">
+      <c r="BW8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BW8" s="30" t="inlineStr">
+      <c r="BX8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BX8" s="30" t="inlineStr">
+      <c r="BY8" s="30" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="BY8" s="30" t="inlineStr">
+      <c r="BZ8" s="30" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="BZ8" s="30" t="inlineStr">
+      <c r="CA8" s="30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="CA8" s="30" t="inlineStr">
+      <c r="CB8" s="30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="CB8" s="30" t="inlineStr">
+      <c r="CC8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="CC8" s="30" t="inlineStr">
+      <c r="CD8" s="30" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="CD8" s="30" t="inlineStr">
+      <c r="CE8" s="30" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="CE8" s="30" t="inlineStr">
+      <c r="CF8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="CF8" s="30" t="inlineStr">
+      <c r="CG8" s="30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="CG8" s="30" t="inlineStr">
+      <c r="CH8" s="30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="CH8" s="30" t="inlineStr">
+      <c r="CI8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="CI8" s="30" t="inlineStr">
+      <c r="CJ8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="CJ8" s="30" t="inlineStr">
+      <c r="CK8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="CK8" s="30" t="inlineStr">
+      <c r="CL8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="CL8" s="30" t="inlineStr">
+      <c r="CM8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="CM8" s="30" t="inlineStr">
+      <c r="CN8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="CN8" s="30" t="inlineStr">
+      <c r="CO8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="CO8" s="30" t="inlineStr">
+      <c r="CP8" s="30" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="CP8" s="30" t="inlineStr">
+      <c r="CQ8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="CQ8" s="30" t="inlineStr">
+      <c r="CR8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="CR8" s="30" t="inlineStr">
+      <c r="CS8" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="CS8" s="30" t="inlineStr">
+      <c r="CT8" s="30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="CT8" s="30" t="inlineStr">
+      <c r="CU8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="CU8" s="30" t="inlineStr">
+      <c r="CV8" s="30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="CV8" s="30" t="inlineStr">
+      <c r="CW8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="CW8" s="30" t="inlineStr">
+      <c r="CX8" s="30" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="CX8" s="30" t="inlineStr">
+      <c r="CY8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="CY8" s="30" t="inlineStr">
+      <c r="CZ8" s="30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="CZ8" s="30" t="inlineStr">
+      <c r="DA8" s="30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="DA8" s="30" t="inlineStr">
+      <c r="DB8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="DB8" s="30" t="inlineStr">
+      <c r="DC8" s="30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="DC8" s="30" t="inlineStr">
+      <c r="DD8" s="30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="DD8" s="30" t="inlineStr">
+      <c r="DE8" s="30" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="DE8" s="30" t="inlineStr">
+      <c r="DF8" s="30" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="DF8" s="30" t="inlineStr">
+      <c r="DG8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="DG8" s="30" t="inlineStr">
+      <c r="DH8" s="30" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="DH8" s="30" t="inlineStr">
+      <c r="DI8" s="30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="DI8" s="30" t="inlineStr">
+      <c r="DJ8" s="30" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="DJ8" s="30" t="inlineStr">
+      <c r="DK8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="DK8" s="30" t="inlineStr">
+      <c r="DL8" s="30" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+      <c r="DM8" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="DN8" s="30" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
